--- a/LAPTOP_TANPA_LINK_AFFILIATE.xlsx
+++ b/LAPTOP_TANPA_LINK_AFFILIATE.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semua" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,19 +15,60 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keterangan" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1E3A8A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -43,22 +83,28 @@
       <color rgb="001E3A8A"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -76,12 +122,82 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -98,19 +214,60 @@
         <color rgb="00D1D5DB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,9 +275,28 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -483,1005 +659,1109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Link Affiliate</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Budget  (6 laptop)</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Budget  (8 laptop)</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Acer Aspire Lite AL14-42P</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n"/>
+      <c r="C3" s="16" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Advan Workmate Ultra Core Ultra 5 115U</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>ASUS ExpertBook P1 Core i3-1315U</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>ASUS VivoBook 15</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="C6" s="16" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Lenovo IdeaPad Slim 3 14IRU8 Core i3-1315U</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="C7" s="16" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Polytron Laptop Luxia i3 1215</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="C8" s="16" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Polytron Luxia Pro i5-1235U</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Produktivitas  (11 laptop)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
+      <c r="C9" s="16" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Polytron Luxia Ryzen 5 7430U</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Produktivitas  (12 laptop)</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Acer Aspire Lite 15 R5-7430U</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="C12" s="16" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Acer Aspire Lite 15 R5-8640HS</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="C13" s="16" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Acer Aspire Lite 15 Ryzen 7 8840HS</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="C14" s="16" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Advan Pixwar Touchscreen Ryzen 7 8745HS</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="C15" s="16" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Advan Workplus Heritage Ryzen 5 7535HS</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="C16" s="16" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Advan Workplus Ryzen 5 6600H</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="C17" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Advan Workplus Ryzen 7 7735HS</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="C18" s="16" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>ASUS ExpertBook PM1403CDA Ryzen 5 150</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="C19" s="16" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Axioo Hype 7 X8 Ryzen 7 6800H</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Produktivitas</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Lenovo IdeaPad Slim 3 14ARP10 Ryzen 5 7535HS</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="C21" s="16" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Lenovo IdeaPad Slim 3 14IRH10 Core i5-13420H</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="C22" s="16" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Polytron Luxia Pro Ultra 5 125H</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Gaming  (14 laptop)</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="C23" s="16" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Gaming  (17 laptop)</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Acer Nitro Lite 16 Core 5 210H RTX 4050</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Acer Nitro Lite 16 Core 7 240H RTX 4050</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Acer Nitro V15 ANV15-42 R7 7445HS</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>ASUS Gaming V16 V3607VH Core 5 210H</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>ASUS TUF A15 FA506NCG</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>ASUS TUF A16 FA608UH RTX 5050</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>ASUS TUF Gaming A16 FA607NUG</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Axioo Pongo 535 i5-13420H RTX 3050</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Axioo Pongo 755 R7 255 RTX 5050</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Axioo Pongo 755-X72 R7 255 RTX 5050</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Colorful Evol P15 RTX 5050</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>HP Victus 15 FA2717TX i5-13420H</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Lenovo LOQ 15AHP10 RTX 5050</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Lenovo LOQ 15AHP11 R7 250 RTX 5050</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Lenovo LOQ 15IRX10 i5-13450HX</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Lenovo LOQ 15IRX10 i7-13700HX</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>Lenovo LOQ 15IRX9 i5-13450HX</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="n"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>High Gaming  (24 laptop)</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>Acer Predator Helios Neo 16S Ultra 7 255HX RTX 5060</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>Acer Predator Helios Neo 16S Ultra 7 356H RTX 5060</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Acer Predator Helios Neo 16S Ultra 9 386H RTX 5070</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>ASUS ROG Strix G16 2025 G614PR RTX 5070 Ti</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>ASUS ROG Strix G16 G614PH Ryzen 9 8940HX RTX 5050</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>ASUS TUF A14 FA401UH Ryzen AI 7 260 RTX 5050</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>ASUS TUF A16 FA608UM Ryzen AI 7 260 RTX 5060</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>ASUS TUF A16 FA608UP Ryzen AI 7 260 RTX 5070</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>Axioo Pongo 765 i7-13620H RTX 5060</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>Axioo Pongo 765 V2 i7-13700H RTX 5060</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>Axioo Pongo 775 i7-13620H RTX 5070</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>HP Omen i7-14650HX RTX 5060</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
         <is>
           <t>HP Omen Max 16 Ryzen AI 7 350 RTX 5070 Ti</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>HP Omen Ryzen 9 8940HX RTX 5060</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>Lenovo Legion 5i 15IAX10 Ultra 7 255HX RTX 5060</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>Lenovo Legion 5i 15IRX10 i7-13650HX RTX 5050</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>Lenovo Legion 5i 15IRX10 i7-14700HX RTX 5060</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="inlineStr">
         <is>
           <t>Lenovo Legion 5i 15IRX10 OLED RTX 5050</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="inlineStr">
         <is>
           <t>Lenovo Legion Pro 5i 16 OLED Ultra 9 275HX RTX 5070 Ti</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
         <is>
           <t>Lenovo LOQ 15AHP11 Ryzen AI 7 250 RTX 5060</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="inlineStr">
         <is>
           <t>MSI Crosshair A16 HX Ryzen 9 7945HX RTX 5060</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
         <is>
           <t>MSI Crosshair A16 HX Ryzen 9 7945HX RTX 5070</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="inlineStr">
         <is>
           <t>MSI Vector 16HX Ultra 7 255HX RTX 5070 Ti</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="inlineStr">
         <is>
           <t>MSI Vector 16HX Ultra 9 275HX RTX 5080</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="n"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Ultrabook  (16 laptop)</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="n"/>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>Ultrabook  (18 laptop)</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="n"/>
+      <c r="C67" s="14" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>Acer Swift 14 OLED Core Ultra 5 226V</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="15" t="inlineStr">
         <is>
           <t>Acer Swift Air 14 Core Ultra 5 125H</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="15" t="inlineStr">
         <is>
           <t>Acer Swift Air 14 Core Ultra 7 155H</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="15" t="inlineStr">
         <is>
           <t>Acer Swift Go 14 AI SFG14-171 Ultra 7 358H</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="inlineStr">
         <is>
           <t>Acer Swift Go 14 SFG14 Ultra 5 125H</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="inlineStr">
         <is>
           <t>Advan Workplus AI Ryzen 7 255</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="15" t="inlineStr">
         <is>
           <t>Apple MacBook Air M2 13&amp;quot;</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="inlineStr">
         <is>
           <t>Apple MacBook Air M4</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="15" t="inlineStr">
         <is>
           <t>Apple MacBook Pro 14 M5</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="inlineStr">
         <is>
           <t>ASUS ExpertBook B9400CBA Ultra 7 358H</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="inlineStr">
         <is>
           <t>ASUS ExpertBook Ultra P5405CSA Ultra 7 258V</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C78" s="16" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="inlineStr">
+        <is>
+          <t>ASUS Vivobook S14 Ryzen 7 260</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C79" s="16" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="inlineStr">
         <is>
           <t>Lenovo IdeaPad Slim 5 14 OLED Ryzen 7 8845HS</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="inlineStr">
         <is>
           <t>Lenovo IdeaPad Slim 5 14IAH10 Ultra 5 225H</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="15" t="inlineStr">
         <is>
           <t>Lenovo IdeaPad Slim 5i Ultra 7 255H</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="inlineStr">
         <is>
           <t>Lenovo Yoga Slim 7i Aura Edition Ultra 5 226V</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="15" t="inlineStr">
         <is>
           <t>MSI Prestige 14 AI+ Ultra 7 355</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C84" s="16" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="inlineStr">
         <is>
           <t>MSI Prestige 14 Flip AI+ Ultra 9 386H</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="n"/>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1494,108 +1774,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Link Affiliate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Acer Aspire Lite AL14-42P</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
+      <c r="C2" s="16" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Advan Workmate Ultra Core Ultra 5 115U</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n"/>
+      <c r="C3" s="16" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>ASUS ExpertBook P1 Core i3-1315U</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>ASUS VivoBook 15</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="C5" s="16" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Lenovo IdeaPad Slim 3 14IRU8 Core i3-1315U</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="C6" s="16" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Polytron Laptop Luxia i3 1215</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="C7" s="16" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Polytron Luxia Pro i5-1235U</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n"/>
+      <c r="C8" s="16" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Polytron Luxia Ryzen 5 7430U</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1608,173 +1914,186 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Link Affiliate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Acer Aspire Lite 15 R5-7430U</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
+      <c r="C2" s="16" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Acer Aspire Lite 15 R5-8640HS</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n"/>
+      <c r="C3" s="16" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Acer Aspire Lite 15 Ryzen 7 8840HS</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Advan Pixwar Touchscreen Ryzen 7 8745HS</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
+      <c r="C5" s="16" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Advan Workplus Heritage Ryzen 5 7535HS</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
+      <c r="C6" s="16" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Advan Workplus Ryzen 5 6600H</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n"/>
+      <c r="C7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Advan Workplus Ryzen 7 7735HS</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
+      <c r="C8" s="16" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>ASUS ExpertBook PM1403CDA Ryzen 5 150</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n"/>
+      <c r="C9" s="16" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Axioo Hype 7 X8 Ryzen 7 6800H</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Produktivitas</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Lenovo IdeaPad Slim 3 14ARP10 Ryzen 5 7535HS</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="C11" s="16" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Lenovo IdeaPad Slim 3 14IRH10 Core i5-13420H</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="C12" s="16" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Polytron Luxia Pro Ultra 5 125H</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Produktivitas</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
+      <c r="C13" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1787,212 +2106,251 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Link Affiliate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Acer Nitro Lite 16 Core 5 210H RTX 4050</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Acer Nitro Lite 16 Core 7 240H RTX 4050</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Acer Nitro V15 ANV15-42 R7 7445HS</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>ASUS Gaming V16 V3607VH Core 5 210H</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>ASUS TUF A15 FA506NCG</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>ASUS TUF A16 FA608UH RTX 5050</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>ASUS TUF Gaming A16 FA607NUG</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Axioo Pongo 535 i5-13420H RTX 3050</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Axioo Pongo 755 R7 255 RTX 5050</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Axioo Pongo 755-X72 R7 255 RTX 5050</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Colorful Evol P15 RTX 5050</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>HP Victus 15 FA2717TX i5-13420H</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Lenovo LOQ 15AHP10 RTX 5050</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Lenovo LOQ 15AHP11 R7 250 RTX 5050</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Lenovo LOQ 15IRX10 i5-13450HX</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Lenovo LOQ 15IRX10 i7-13700HX</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Lenovo LOQ 15IRX9 i5-13450HX</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n"/>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2008,339 +2366,339 @@
   <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Link Affiliate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Acer Predator Helios Neo 16S Ultra 7 255HX RTX 5060</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n"/>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Acer Predator Helios Neo 16S Ultra 7 356H RTX 5060</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n"/>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Acer Predator Helios Neo 16S Ultra 9 386H RTX 5070</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>ASUS ROG Strix G16 2025 G614PR RTX 5070 Ti</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>ASUS ROG Strix G16 G614PH Ryzen 9 8940HX RTX 5050</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n"/>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>ASUS TUF A14 FA401UH Ryzen AI 7 260 RTX 5050</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n"/>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>ASUS TUF A16 FA608UM Ryzen AI 7 260 RTX 5060</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n"/>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>ASUS TUF A16 FA608UP Ryzen AI 7 260 RTX 5070</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n"/>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Axioo Pongo 765 i7-13620H RTX 5060</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Axioo Pongo 765 V2 i7-13700H RTX 5060</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n"/>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Axioo Pongo 775 i7-13620H RTX 5070</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n"/>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>HP Omen i7-14650HX RTX 5060</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n"/>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>HP Omen Max 16 Ryzen AI 7 350 RTX 5070 Ti</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n"/>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>HP Omen Ryzen 9 8940HX RTX 5060</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n"/>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Lenovo Legion 5i 15IAX10 Ultra 7 255HX RTX 5060</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n"/>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Lenovo Legion 5i 15IRX10 i7-13650HX RTX 5050</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n"/>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Lenovo Legion 5i 15IRX10 i7-14700HX RTX 5060</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n"/>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Lenovo Legion 5i 15IRX10 OLED RTX 5050</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n"/>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Lenovo Legion Pro 5i 16 OLED Ultra 9 275HX RTX 5070 Ti</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n"/>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Lenovo LOQ 15AHP11 Ryzen AI 7 250 RTX 5060</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n"/>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>MSI Crosshair A16 HX Ryzen 9 7945HX RTX 5060</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n"/>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>MSI Crosshair A16 HX Ryzen 9 7945HX RTX 5070</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n"/>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>MSI Vector 16HX Ultra 7 255HX RTX 5070 Ti</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n"/>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>MSI Vector 16HX Ultra 9 275HX RTX 5080</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n"/>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2353,238 +2711,264 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Link Affiliate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Acer Swift 14 OLED Core Ultra 5 226V</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Acer Swift Air 14 Core Ultra 5 125H</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Acer Swift Air 14 Core Ultra 7 155H</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Acer Swift Go 14 AI SFG14-171 Ultra 7 358H</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Acer Swift Go 14 SFG14 Ultra 5 125H</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Advan Workplus AI Ryzen 7 255</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Apple MacBook Air M2 13&amp;quot;</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Apple MacBook Air M4</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Apple MacBook Pro 14 M5</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>ASUS ExpertBook B9400CBA Ultra 7 358H</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>ASUS ExpertBook Ultra P5405CSA Ultra 7 258V</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>ASUS Vivobook S14 Ryzen 7 260</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Lenovo IdeaPad Slim 5 14 OLED Ryzen 7 8845HS</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Lenovo IdeaPad Slim 5 14IAH10 Ultra 5 225H</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Lenovo IdeaPad Slim 5i Ultra 7 255H</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Lenovo Yoga Slim 7i Aura Edition Ultra 5 226V</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>MSI Prestige 14 AI+ Ultra 7 355</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>MSI Prestige 14 Flip AI+ Ultra 9 386H</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n"/>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2597,150 +2981,174 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Isi file ini</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Daftar laptop AstroLaptop yang BELUM punya link affiliate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Tanggal dibuat</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>10 Agustus 2026</t>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>13 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Sumber data</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Halaman review di src/pages/review/ (prop linkTokopedia &amp; linkShopee)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr"/>
-      <c r="B4" s="7" t="inlineStr"/>
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Total halaman review</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>81</t>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Sudah punya link</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>BELUM punya link</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>71  &lt;- isi file ini</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>79  &lt;- isi file ini</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr"/>
-      <c r="B8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Cara mengisi</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Isi kolom "Link Affiliate" (sel berlatar kuning). Kolom Laptop dan Kategori jangan diubah</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Contoh format link</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>https://tk.tokopedia.com/ZS4vF7kpy/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Setelah diisi</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Kirim file ini kembali, link akan dipasang ke tombol beli di tiap halaman review</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr"/>
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Struktur sheet</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Semua = seluruh 71 laptop dikelompokkan per kategori</t>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Semua = seluruh 79 laptop dikelompokkan per kategori</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr"/>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Budget / Produktivitas / Gaming / High Gaming / Ultrabook = terpisah per kategori</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Catatan</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Daftar ini diperbarui 13 Agustus 2026 seiring bertambahnya laptop di project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Project kini 89 laptop setelah Polytron Luxia Ryzen 5 7430U ditambahkan (13 Agustus 2026).</t>
         </is>
       </c>
     </row>

--- a/LAPTOP_TANPA_LINK_AFFILIATE.xlsx
+++ b/LAPTOP_TANPA_LINK_AFFILIATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cahya\OneDrive\Documents\Claude\Projects\astro-laptop-latihan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C57CBF6-F0CB-4C58-ABA3-28F94E86C2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6801FACC-3666-4DCE-9DCA-CBA52798CF00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/LAPTOP_TANPA_LINK_AFFILIATE.xlsx
+++ b/LAPTOP_TANPA_LINK_AFFILIATE.xlsx
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -1861,7 +1861,7 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>Ultrabook  (19 laptop)</t>
+          <t>Ultrabook  (20 laptop)</t>
         </is>
       </c>
       <c r="B77" s="11" t="n"/>
@@ -2060,7 +2060,7 @@
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5 14 OLED Ryzen 7 8845HS</t>
+          <t>HP OmniBook 3 14 Core 3 100U</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -2069,12 +2069,15 @@
         </is>
       </c>
       <c r="C91" s="6" t="n"/>
+      <c r="D91" t="n">
+        <v>12.5</v>
+      </c>
       <c r="E91" s="9" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5 14IAH10 Ultra 5 225H</t>
+          <t>Lenovo IdeaPad Slim 5 14 OLED Ryzen 7 8845HS</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -2088,7 +2091,7 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5i Ultra 7 255H</t>
+          <t>Lenovo IdeaPad Slim 5 14IAH10 Ultra 5 225H</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -2102,7 +2105,7 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7i Aura Edition Ultra 5 226V</t>
+          <t>Lenovo IdeaPad Slim 5i Ultra 7 255H</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -2116,7 +2119,7 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>MSI Prestige 14 AI+ Ultra 7 355</t>
+          <t>Lenovo Yoga Slim 7i Aura Edition Ultra 5 226V</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -2130,7 +2133,7 @@
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>MSI Prestige 14 Flip AI+ Ultra 9 386H</t>
+          <t>MSI Prestige 14 AI+ Ultra 7 355</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -2140,6 +2143,20 @@
       </c>
       <c r="C96" s="6" t="n"/>
       <c r="E96" s="9" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>MSI Prestige 14 Flip AI+ Ultra 9 386H</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="n"/>
+      <c r="E97" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3520,7 +3537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3732,7 +3749,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5 14 OLED Ryzen 7 8845HS</t>
+          <t>HP OmniBook 3 14 Core 3 100U</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -3745,7 +3762,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5 14IAH10 Ultra 5 225H</t>
+          <t>Lenovo IdeaPad Slim 5 14 OLED Ryzen 7 8845HS</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -3758,7 +3775,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5i Ultra 7 255H</t>
+          <t>Lenovo IdeaPad Slim 5 14IAH10 Ultra 5 225H</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -3771,7 +3788,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7i Aura Edition Ultra 5 226V</t>
+          <t>Lenovo IdeaPad Slim 5i Ultra 7 255H</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -3784,7 +3801,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>MSI Prestige 14 AI+ Ultra 7 355</t>
+          <t>Lenovo Yoga Slim 7i Aura Edition Ultra 5 226V</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -3797,15 +3814,28 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>MSI Prestige 14 AI+ Ultra 7 355</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>MSI Prestige 14 Flip AI+ Ultra 9 386H</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Ultrabook</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/LAPTOP_TANPA_LINK_AFFILIATE.xlsx
+++ b/LAPTOP_TANPA_LINK_AFFILIATE.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="30612" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semua" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,8 +69,14 @@
       <color rgb="FF047857"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF047857"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +101,23 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -180,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -204,6 +227,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -569,14 +602,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="10" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="13.08984375" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="46.54296875" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -597,7 +630,7 @@
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>Harga</t>
+          <t>Harga Latest</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -614,9 +647,15 @@
       </c>
       <c r="B2" s="11" t="n"/>
       <c r="C2" s="12" t="n"/>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>Dalam Juta</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Baru di tambah</t>
         </is>
       </c>
     </row>
@@ -819,6 +858,7 @@
       </c>
       <c r="B12" s="11" t="n"/>
       <c r="C12" s="12" t="n"/>
+      <c r="D12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -925,6 +965,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="9" t="n"/>
+      <c r="G17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -1094,11 +1135,12 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Gaming  (25 laptop)</t>
+          <t>Gaming  (24 laptop)</t>
         </is>
       </c>
       <c r="B26" s="11" t="n"/>
       <c r="C26" s="12" t="n"/>
+      <c r="D26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -1133,7 +1175,14 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n"/>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVrKT7Fy/</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>17.7</v>
+      </c>
       <c r="E28" s="9" t="n"/>
     </row>
     <row r="29">
@@ -1147,13 +1196,24 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n"/>
-      <c r="E29" s="9" t="n"/>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVrErsTB/</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Acer Nitro Lite NL16</t>
+          <t>Acer Nitro Lite NL16 3050</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -1183,7 +1243,14 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C31" s="6" t="n"/>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVrEQuNE/</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>16.7</v>
+      </c>
       <c r="E31" s="9" t="n"/>
     </row>
     <row r="32">
@@ -1233,7 +1300,14 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C34" s="6" t="n"/>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVrEvhme/</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13.4</v>
+      </c>
       <c r="E34" s="9" t="n"/>
     </row>
     <row r="35">
@@ -1247,7 +1321,14 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C35" s="6" t="n"/>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVrEtTrs/</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>24.3</v>
+      </c>
       <c r="E35" s="9" t="n"/>
     </row>
     <row r="36">
@@ -1261,7 +1342,14 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C36" s="6" t="n"/>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVroFR3P/</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E36" s="9" t="n"/>
     </row>
     <row r="37">
@@ -1297,9 +1385,9 @@
       <c r="E38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>Axioo Pongo 755 R7 255 RTX 5050</t>
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>Axioo Pongo 755-X72 R7 255 RTX 5050</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -1308,7 +1396,7 @@
         </is>
       </c>
       <c r="C39" s="6" t="n"/>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E39" s="18" t="inlineStr">
         <is>
           <t>Hot Deals</t>
         </is>
@@ -1317,7 +1405,7 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Axioo Pongo 755-X72 R7 255 RTX 5050</t>
+          <t>Colorful Evol P15 HE55D i5-12450H</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -1325,13 +1413,21 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C40" s="6" t="n"/>
-      <c r="E40" s="9" t="n"/>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZS4tEaS7p/</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>Hot Deals</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Colorful Evol P15 HE55D i5-12450H</t>
+          <t>Colorful Evol P15 RTX 5050</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -1339,11 +1435,7 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>https://tk.tokopedia.com/ZS4tEaS7p/</t>
-        </is>
-      </c>
+      <c r="C41" s="6" t="n"/>
       <c r="E41" s="9" t="inlineStr">
         <is>
           <t>Hot Deals</t>
@@ -1353,7 +1445,7 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>Colorful Evol P15 RTX 5050</t>
+          <t>HP Victus 15 FA2717TX i5-13420H</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -1362,16 +1454,12 @@
         </is>
       </c>
       <c r="C42" s="6" t="n"/>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>Hot Deals</t>
-        </is>
-      </c>
+      <c r="E42" s="9" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>HP Victus 15 FA2717TX i5-13420H</t>
+          <t>HP Victus 15 i5-13420H RTX 3050</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -1380,12 +1468,15 @@
         </is>
       </c>
       <c r="C43" s="6" t="n"/>
+      <c r="D43" t="n">
+        <v>15.489</v>
+      </c>
       <c r="E43" s="9" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>HP Victus 15 i5-13420H RTX 3050</t>
+          <t>Lenovo LOQ 15AHP10 RTX 5050</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -1394,15 +1485,12 @@
         </is>
       </c>
       <c r="C44" s="6" t="n"/>
-      <c r="D44" t="n">
-        <v>15.489</v>
-      </c>
       <c r="E44" s="9" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15AHP10 RTX 5050</t>
+          <t>Lenovo LOQ 15AHP11 R7 250 RTX 5050</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -1416,7 +1504,7 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15AHP11 R7 250 RTX 5050</t>
+          <t>Lenovo LOQ 15ARP10E Ryzen 7 170 RTX 3050</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -1424,13 +1512,17 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C46" s="6" t="n"/>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZS4vF7kpy/</t>
+        </is>
+      </c>
       <c r="E46" s="9" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15ARP10E Ryzen 7 170 RTX 3050</t>
+          <t>Lenovo LOQ 15IRX10 i5-13450HX</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -1438,17 +1530,17 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>https://tk.tokopedia.com/ZS4vF7kpy/</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>Hot Deals</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15IRX10 i5-13450HX</t>
+          <t>Lenovo LOQ 15IRX10 i7-13700HX</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -1457,16 +1549,12 @@
         </is>
       </c>
       <c r="C48" s="6" t="n"/>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>Hot Deals</t>
-        </is>
-      </c>
+      <c r="E48" s="9" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15IRX10 i7-13700HX</t>
+          <t>Lenovo LOQ 15IRX9 i5-13450HX</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -1480,7 +1568,7 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15IRX9 i5-13450HX</t>
+          <t>Lenovo LOQ Essential 15ARP10E R7 7735HS</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -1488,44 +1576,45 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C50" s="6" t="n"/>
-      <c r="E50" s="9" t="n"/>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZS4tEVArt/</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>Hot Deals</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>Lenovo LOQ Essential 15ARP10E R7 7735HS</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>https://tk.tokopedia.com/ZS4tEVArt/</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>Hot Deals</t>
-        </is>
-      </c>
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>High Gaming  (24 laptop)</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n"/>
+      <c r="C51" s="12" t="n"/>
+      <c r="D51" s="14" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>High Gaming  (24 laptop)</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="n"/>
-      <c r="C52" s="12" t="n"/>
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Acer Predator Helios Neo 16S Ultra 7 255HX RTX 5060</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n"/>
+      <c r="E52" s="9" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>Acer Predator Helios Neo 16S Ultra 7 255HX RTX 5060</t>
+          <t>Acer Predator Helios Neo 16S Ultra 7 356H RTX 5060</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -1539,7 +1628,7 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>Acer Predator Helios Neo 16S Ultra 7 356H RTX 5060</t>
+          <t>Acer Predator Helios Neo 16S Ultra 9 386H RTX 5070</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -1553,7 +1642,7 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>Acer Predator Helios Neo 16S Ultra 9 386H RTX 5070</t>
+          <t>ASUS ROG Strix G16 2025 G614PR RTX 5070 Ti</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -1567,7 +1656,7 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>ASUS ROG Strix G16 2025 G614PR RTX 5070 Ti</t>
+          <t>ASUS ROG Strix G16 G614PH Ryzen 9 8940HX RTX 5050</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -1581,7 +1670,7 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>ASUS ROG Strix G16 G614PH Ryzen 9 8940HX RTX 5050</t>
+          <t>ASUS TUF A14 FA401UH Ryzen AI 7 260 RTX 5050</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -1595,7 +1684,7 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>ASUS TUF A14 FA401UH Ryzen AI 7 260 RTX 5050</t>
+          <t>ASUS TUF A16 FA608UM Ryzen AI 7 260 RTX 5060</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -1609,7 +1698,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>ASUS TUF A16 FA608UM Ryzen AI 7 260 RTX 5060</t>
+          <t>ASUS TUF A16 FA608UP Ryzen AI 7 260 RTX 5070</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -1623,7 +1712,7 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>ASUS TUF A16 FA608UP Ryzen AI 7 260 RTX 5070</t>
+          <t>Axioo Pongo 765 i7-13620H RTX 5060</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -1637,7 +1726,7 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>Axioo Pongo 765 i7-13620H RTX 5060</t>
+          <t>Axioo Pongo 765 V2 i7-13700H RTX 5060</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -1651,7 +1740,7 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>Axioo Pongo 765 V2 i7-13700H RTX 5060</t>
+          <t>Axioo Pongo 775 i7-13620H RTX 5070</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -1665,7 +1754,7 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>Axioo Pongo 775 i7-13620H RTX 5070</t>
+          <t>HP Omen i7-14650HX RTX 5060</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -1679,7 +1768,7 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>HP Omen i7-14650HX RTX 5060</t>
+          <t>HP Omen Max 16 Ryzen AI 7 350 RTX 5070 Ti</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -1693,7 +1782,7 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>HP Omen Max 16 Ryzen AI 7 350 RTX 5070 Ti</t>
+          <t>HP Omen Ryzen 9 8940HX RTX 5060</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -1707,7 +1796,7 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>HP Omen Ryzen 9 8940HX RTX 5060</t>
+          <t>Lenovo Legion 5i 15IAX10 Ultra 7 255HX RTX 5060</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -1721,7 +1810,7 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>Lenovo Legion 5i 15IAX10 Ultra 7 255HX RTX 5060</t>
+          <t>Lenovo Legion 5i 15IRX10 i7-13650HX RTX 5050</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -1735,7 +1824,7 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>Lenovo Legion 5i 15IRX10 i7-13650HX RTX 5050</t>
+          <t>Lenovo Legion 5i 15IRX10 i7-14700HX RTX 5060</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -1749,7 +1838,7 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>Lenovo Legion 5i 15IRX10 i7-14700HX RTX 5060</t>
+          <t>Lenovo Legion 5i 15IRX10 OLED RTX 5050</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -1763,7 +1852,7 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>Lenovo Legion 5i 15IRX10 OLED RTX 5050</t>
+          <t>Lenovo Legion Pro 5i 16 OLED Ultra 9 275HX RTX 5070 Ti</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -1777,7 +1866,7 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5i 16 OLED Ultra 9 275HX RTX 5070 Ti</t>
+          <t>Lenovo LOQ 15AHP11 Ryzen AI 7 250 RTX 5060</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -1791,7 +1880,7 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15AHP11 Ryzen AI 7 250 RTX 5060</t>
+          <t>MSI Crosshair A16 HX Ryzen 9 7945HX RTX 5060</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -1805,7 +1894,7 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>MSI Crosshair A16 HX Ryzen 9 7945HX RTX 5060</t>
+          <t>MSI Crosshair A16 HX Ryzen 9 7945HX RTX 5070</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -1819,7 +1908,7 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>MSI Crosshair A16 HX Ryzen 9 7945HX RTX 5070</t>
+          <t>MSI Vector 16HX Ultra 7 255HX RTX 5070 Ti</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -1833,7 +1922,7 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>MSI Vector 16HX Ultra 7 255HX RTX 5070 Ti</t>
+          <t>MSI Vector 16HX Ultra 9 275HX RTX 5080</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -1845,32 +1934,33 @@
       <c r="E75" s="9" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>MSI Vector 16HX Ultra 9 275HX RTX 5080</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="n"/>
-      <c r="E76" s="9" t="n"/>
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>Ultrabook  (20 laptop)</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n"/>
+      <c r="C76" s="12" t="n"/>
+      <c r="D76" s="14" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>Ultrabook  (20 laptop)</t>
-        </is>
-      </c>
-      <c r="B77" s="11" t="n"/>
-      <c r="C77" s="12" t="n"/>
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>Acer Swift 14 OLED Core Ultra 5 226V</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="n"/>
+      <c r="E77" s="9" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>Acer Swift 14 OLED Core Ultra 5 226V</t>
+          <t>Acer Swift Air 14 Core Ultra 5 125H</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -1884,7 +1974,7 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>Acer Swift Air 14 Core Ultra 5 125H</t>
+          <t>Acer Swift Air 14 Core Ultra 7 155H</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -1898,7 +1988,7 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>Acer Swift Air 14 Core Ultra 7 155H</t>
+          <t>Acer Swift Go 14 AI SFG14-171 Ultra 7 358H</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -1912,7 +2002,7 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>Acer Swift Go 14 AI SFG14-171 Ultra 7 358H</t>
+          <t>Acer Swift Go 14 AI SFG14-73-73P9</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -1920,13 +2010,21 @@
           <t>Ultrabook</t>
         </is>
       </c>
-      <c r="C81" s="6" t="n"/>
-      <c r="E81" s="9" t="n"/>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZS4tos6XL/</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>Hot Deals</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>Acer Swift Go 14 AI SFG14-73-73P9</t>
+          <t>Acer Swift Go 14 SFG14 Ultra 5 125H</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -1934,21 +2032,13 @@
           <t>Ultrabook</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>https://tk.tokopedia.com/ZS4tos6XL/</t>
-        </is>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>Hot Deals</t>
-        </is>
-      </c>
+      <c r="C82" s="6" t="n"/>
+      <c r="E82" s="9" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>Acer Swift Go 14 SFG14 Ultra 5 125H</t>
+          <t>Advan Workplus AI Ryzen 7 255</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -1962,7 +2052,7 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>Advan Workplus AI Ryzen 7 255</t>
+          <t>Apple MacBook Air M2 13&amp;quot;</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -1976,7 +2066,7 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>Apple MacBook Air M2 13&amp;quot;</t>
+          <t>Apple MacBook Air M4</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -1990,7 +2080,7 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>Apple MacBook Air M4</t>
+          <t>Apple MacBook Pro 14 M5</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -2004,7 +2094,7 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>Apple MacBook Pro 14 M5</t>
+          <t>ASUS ExpertBook B9400CBA Ultra 7 358H</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
@@ -2018,7 +2108,7 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>ASUS ExpertBook B9400CBA Ultra 7 358H</t>
+          <t>ASUS ExpertBook Ultra P5405CSA Ultra 7 258V</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -2032,7 +2122,7 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>ASUS ExpertBook Ultra P5405CSA Ultra 7 258V</t>
+          <t>ASUS Vivobook S14 Ryzen 7 260</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -2046,7 +2136,7 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14 Ryzen 7 260</t>
+          <t>HP OmniBook 3 14 Core 3 100U</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -2055,12 +2145,15 @@
         </is>
       </c>
       <c r="C90" s="6" t="n"/>
+      <c r="D90" t="n">
+        <v>12.5</v>
+      </c>
       <c r="E90" s="9" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>HP OmniBook 3 14 Core 3 100U</t>
+          <t>Lenovo IdeaPad Slim 5 14 OLED Ryzen 7 8845HS</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -2069,15 +2162,12 @@
         </is>
       </c>
       <c r="C91" s="6" t="n"/>
-      <c r="D91" t="n">
-        <v>12.5</v>
-      </c>
       <c r="E91" s="9" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5 14 OLED Ryzen 7 8845HS</t>
+          <t>Lenovo IdeaPad Slim 5 14IAH10 Ultra 5 225H</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -2091,7 +2181,7 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5 14IAH10 Ultra 5 225H</t>
+          <t>Lenovo IdeaPad Slim 5i Ultra 7 255H</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -2105,7 +2195,7 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5i Ultra 7 255H</t>
+          <t>Lenovo Yoga Slim 7i Aura Edition Ultra 5 226V</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -2119,7 +2209,7 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7i Aura Edition Ultra 5 226V</t>
+          <t>MSI Prestige 14 AI+ Ultra 7 355</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -2133,7 +2223,7 @@
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>MSI Prestige 14 AI+ Ultra 7 355</t>
+          <t>MSI Prestige 14 Flip AI+ Ultra 9 386H</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -2144,27 +2234,13 @@
       <c r="C96" s="6" t="n"/>
       <c r="E96" s="9" t="n"/>
     </row>
-    <row r="97">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>MSI Prestige 14 Flip AI+ Ultra 9 386H</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="n"/>
-      <c r="E97" s="9" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A76:C76"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A51:C51"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
@@ -2188,13 +2264,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2722,7 +2804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -2786,7 +2868,11 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVrKT7Fy/</t>
+        </is>
+      </c>
       <c r="D3" s="9" t="n"/>
     </row>
     <row r="4">
@@ -2800,13 +2886,21 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="9" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVrErsTB/</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Acer Nitro Lite NL16</t>
+          <t>Acer Nitro Lite NL16 3050</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -2836,7 +2930,11 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVrEQuNE/</t>
+        </is>
+      </c>
       <c r="D6" s="9" t="n"/>
     </row>
     <row r="7">
@@ -2886,7 +2984,11 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVrEvhme/</t>
+        </is>
+      </c>
       <c r="D9" s="9" t="n"/>
     </row>
     <row r="10">
@@ -2900,7 +3002,11 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVrEtTrs/</t>
+        </is>
+      </c>
       <c r="D10" s="9" t="n"/>
     </row>
     <row r="11">
@@ -2914,7 +3020,11 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVroFR3P/</t>
+        </is>
+      </c>
       <c r="D11" s="9" t="n"/>
     </row>
     <row r="12">
@@ -2950,9 +3060,9 @@
       <c r="D13" s="9" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Axioo Pongo 755 R7 255 RTX 5050</t>
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Axioo Pongo 755-X72 R7 255 RTX 5050</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -2961,7 +3071,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n"/>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>Hot Deals</t>
         </is>
@@ -2970,7 +3080,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Axioo Pongo 755-X72 R7 255 RTX 5050</t>
+          <t>Colorful Evol P15 HE55D i5-12450H</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -2978,13 +3088,21 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="9" t="n"/>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZS4tEaS7p/</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Hot Deals</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Colorful Evol P15 HE55D i5-12450H</t>
+          <t>Colorful Evol P15 RTX 5050</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -2992,11 +3110,7 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>https://tk.tokopedia.com/ZS4tEaS7p/</t>
-        </is>
-      </c>
+      <c r="C16" s="6" t="n"/>
       <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Hot Deals</t>
@@ -3006,7 +3120,7 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Colorful Evol P15 RTX 5050</t>
+          <t>HP Victus 15 FA2717TX i5-13420H</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -3015,16 +3129,12 @@
         </is>
       </c>
       <c r="C17" s="6" t="n"/>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Hot Deals</t>
-        </is>
-      </c>
+      <c r="D17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>HP Victus 15 FA2717TX i5-13420H</t>
+          <t>HP Victus 15 i5-13420H RTX 3050</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -3038,7 +3148,7 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>HP Victus 15 i5-13420H RTX 3050</t>
+          <t>Lenovo LOQ 15AHP10 RTX 5050</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -3052,7 +3162,7 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15AHP10 RTX 5050</t>
+          <t>Lenovo LOQ 15AHP11 R7 250 RTX 5050</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -3066,7 +3176,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15AHP11 R7 250 RTX 5050</t>
+          <t>Lenovo LOQ 15ARP10E Ryzen 7 170 RTX 3050</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -3074,13 +3184,17 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZS4vF7kpy/</t>
+        </is>
+      </c>
       <c r="D21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15ARP10E Ryzen 7 170 RTX 3050</t>
+          <t>Lenovo LOQ 15IRX10 i5-13450HX</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -3088,17 +3202,17 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>https://tk.tokopedia.com/ZS4vF7kpy/</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Hot Deals</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15IRX10 i5-13450HX</t>
+          <t>Lenovo LOQ 15IRX10 i7-13700HX</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -3107,16 +3221,12 @@
         </is>
       </c>
       <c r="C23" s="6" t="n"/>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Hot Deals</t>
-        </is>
-      </c>
+      <c r="D23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15IRX10 i7-13700HX</t>
+          <t>Lenovo LOQ 15IRX9 i5-13450HX</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -3130,7 +3240,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15IRX9 i5-13450HX</t>
+          <t>Lenovo LOQ Essential 15ARP10E R7 7735HS</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -3138,26 +3248,12 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="9" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Lenovo LOQ Essential 15ARP10E R7 7735HS</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>https://tk.tokopedia.com/ZS4tEVArt/</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Hot Deals</t>
         </is>
@@ -3166,12 +3262,18 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LAPTOP_TANPA_LINK_AFFILIATE.xlsx
+++ b/LAPTOP_TANPA_LINK_AFFILIATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cahya\OneDrive\Documents\Claude\Projects\astro-laptop-latihan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAA24A6-96A2-4BF6-8871-C23F08DEC532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EAF88C-547F-4ABF-80E2-FE6568B4F49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -593,7 +593,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -635,6 +635,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -700,7 +706,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -723,7 +729,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -734,6 +739,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1064,11 +1071,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="17"/>
       <c r="D2" s="11" t="s">
         <v>6</v>
       </c>
@@ -1211,11 +1218,11 @@
       <c r="E11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="18"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
       <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -1291,7 +1298,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="9"/>
-      <c r="G17" s="13"/>
+      <c r="G17" s="12"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
@@ -1411,11 +1418,11 @@
       <c r="E25" s="9"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="18"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
       <c r="D26" s="11"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -1439,10 +1446,10 @@
       <c r="B28" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="19">
         <v>17.7</v>
       </c>
       <c r="E28" s="9"/>
@@ -1454,10 +1461,10 @@
       <c r="B29" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="19">
         <v>16.600000000000001</v>
       </c>
       <c r="E29" s="9" t="s">
@@ -1471,9 +1478,10 @@
       <c r="B30" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="18" t="s">
         <v>67</v>
       </c>
+      <c r="D30" s="19"/>
       <c r="E30" s="9" t="s">
         <v>11</v>
       </c>
@@ -1485,10 +1493,10 @@
       <c r="B31" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="19">
         <v>16.7</v>
       </c>
       <c r="E31" s="9"/>
@@ -1500,9 +1508,10 @@
       <c r="B32" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="18" t="s">
         <v>71</v>
       </c>
+      <c r="D32" s="19"/>
       <c r="E32" s="9" t="s">
         <v>11</v>
       </c>
@@ -1514,7 +1523,8 @@
       <c r="B33" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="6"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="19"/>
       <c r="E33" s="9"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -1524,10 +1534,10 @@
       <c r="B34" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="19">
         <v>13.4</v>
       </c>
       <c r="E34" s="9"/>
@@ -1539,10 +1549,10 @@
       <c r="B35" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="19">
         <v>24.3</v>
       </c>
       <c r="E35" s="9"/>
@@ -1554,10 +1564,10 @@
       <c r="B36" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="19">
         <v>20.5</v>
       </c>
       <c r="E36" s="9"/>
@@ -1585,14 +1595,14 @@
       <c r="E38" s="9"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="13" t="s">
         <v>82</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C39" s="6"/>
-      <c r="E39" s="15" t="s">
+      <c r="E39" s="14" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1724,11 +1734,11 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B51" s="17"/>
-      <c r="C51" s="18"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="17"/>
       <c r="D51" s="11"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
@@ -1972,11 +1982,11 @@
       <c r="E75" s="9"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="B76" s="17"/>
-      <c r="C76" s="18"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="17"/>
       <c r="D76" s="11"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
@@ -2762,14 +2772,14 @@
       <c r="D13" s="9"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="13" t="s">
         <v>82</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="6"/>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="14" t="s">
         <v>11</v>
       </c>
     </row>

--- a/LAPTOP_TANPA_LINK_AFFILIATE.xlsx
+++ b/LAPTOP_TANPA_LINK_AFFILIATE.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,14 +69,8 @@
       <color rgb="FF047857"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF047857"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -117,12 +111,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="3" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -209,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -233,17 +222,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -609,17 +594,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="54" customWidth="1" style="19" min="1" max="1"/>
-    <col width="18" customWidth="1" style="19" min="2" max="2"/>
-    <col width="46" customWidth="1" style="19" min="3" max="3"/>
-    <col width="13.08984375" bestFit="1" customWidth="1" style="19" min="4" max="4"/>
-    <col width="46.54296875" bestFit="1" customWidth="1" style="19" min="5" max="5"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="13.08984375" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="46.54296875" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" s="19">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Laptop</t>
@@ -646,17 +631,17 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1" s="19">
-      <c r="A2" s="15" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Budget  (9 laptop)</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="17" t="n"/>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="15" t="n"/>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>Dalam Juta</t>
+          <t>Dalam Juta RP</t>
         </is>
       </c>
       <c r="G2" s="10" t="n"/>
@@ -836,7 +821,7 @@
       </c>
       <c r="E10" s="9" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1" s="19">
+    <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Polytron Luxia Ryzen 5 7430U</t>
@@ -858,13 +843,13 @@
       <c r="E11" s="9" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Produktivitas  (13 laptop)</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="17" t="n"/>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="15" t="n"/>
       <c r="D12" s="11" t="n"/>
     </row>
     <row r="13">
@@ -1097,7 +1082,7 @@
       </c>
       <c r="E23" s="9" t="n"/>
     </row>
-    <row r="24" ht="20" customHeight="1" s="19">
+    <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Lenovo IdeaPad Slim 3 14IRH10 Core i5-13420H</t>
@@ -1140,13 +1125,13 @@
       <c r="E25" s="9" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Gaming  (25 laptop)</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="17" t="n"/>
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Gaming  (26 laptop)</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="15" t="n"/>
       <c r="D26" s="11" t="n"/>
     </row>
     <row r="27">
@@ -1263,7 +1248,7 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Acer Nitro V15 RTX 5050 i5-13420H</t>
+          <t>Acer Nitro V15 Core 5 210H RTX 3050</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -1271,21 +1256,13 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>https://tk.tokopedia.com/ZS4too9ra/</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>Hot Deals</t>
-        </is>
-      </c>
+      <c r="C32" s="6" t="n"/>
+      <c r="E32" s="9" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>ASUS Gaming V16 V3607VH Core 5 210H</t>
+          <t>Acer Nitro V15 RTX 5050 i5-13420H</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -1293,13 +1270,21 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C33" s="6" t="n"/>
-      <c r="E33" s="9" t="n"/>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZS4too9ra/</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>Hot Deals</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>ASUS TUF A15 FA506NCG</t>
+          <t>ASUS Gaming V16 V3607VH Core 5 210H</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -1307,20 +1292,13 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>https://tk.tokopedia.com/ZSVrEvhme/</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="C34" s="6" t="n"/>
       <c r="E34" s="9" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>ASUS TUF A16 FA608UH RTX 5050</t>
+          <t>ASUS TUF A15 FA506NCG</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -1330,18 +1308,18 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>https://tk.tokopedia.com/ZSVrEtTrs/</t>
+          <t>https://tk.tokopedia.com/ZSVrEvhme/</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>24.3</v>
+        <v>13.4</v>
       </c>
       <c r="E35" s="9" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>ASUS TUF Gaming A16 FA607NUG</t>
+          <t>ASUS TUF A16 FA608UH RTX 5050</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -1351,18 +1329,18 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>https://tk.tokopedia.com/ZSVroFR3P/</t>
+          <t>https://tk.tokopedia.com/ZSVrEtTrs/</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>20.5</v>
+        <v>24.3</v>
       </c>
       <c r="E36" s="9" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Axioo Pongo 535 i5-13420H RTX 3050</t>
+          <t>ASUS TUF Gaming A16 FA607NUG</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -1370,13 +1348,20 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C37" s="6" t="n"/>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVroFR3P/</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E37" s="9" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Axioo Pongo 735 i7-13620H RTX 3050</t>
+          <t>Axioo Pongo 535 i5-13420H RTX 3050</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -1390,7 +1375,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Axioo Pongo 750 i7-13620H RTX 4050</t>
+          <t>Axioo Pongo 735 i7-13620H RTX 3050</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -1400,15 +1385,18 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>https://tk.tokopedia.com/ZS4vFaySC/</t>
-        </is>
+          <t>https://tk.tokopedia.com/ZSVUSQLfk/</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>13</v>
       </c>
       <c r="E39" s="9" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Axioo Pongo 755-X72 R7 255 RTX 5050</t>
+          <t>Axioo Pongo 750 i7-13620H RTX 4050</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -1416,47 +1404,60 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C40" s="6" t="n"/>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>Hot Deals</t>
-        </is>
-      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVUSqCs3/</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="E40" s="9" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
+          <t>Axioo Pongo 755-X72 R7 255 RTX 5050</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVUSnmBv/</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>19</v>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>Hot Deals</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
           <t>Colorful Evol P15 HE55D i5-12450H</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>https://tk.tokopedia.com/ZS4tEaS7p/</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>Hot Deals</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1" s="19">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>Colorful Evol P15 RTX 5050</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="n"/>
+      <c r="D42" t="n">
+        <v>15.5</v>
+      </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
           <t>Hot Deals</t>
@@ -1466,7 +1467,7 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>HP Victus 15 FA2717TX i5-13420H</t>
+          <t>Colorful Evol P15 RTX 5050</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -1474,13 +1475,24 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C43" s="6" t="n"/>
-      <c r="E43" s="9" t="n"/>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVUADx7M/</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>19</v>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>Hot Deals</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>HP Victus 15 i5-13420H RTX 3050</t>
+          <t>HP Victus 15 FA2717TX i5-13420H</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -1489,15 +1501,12 @@
         </is>
       </c>
       <c r="C44" s="6" t="n"/>
-      <c r="D44" t="n">
-        <v>15.4</v>
-      </c>
       <c r="E44" s="9" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15AHP10 RTX 5050</t>
+          <t>HP Victus 15 i5-13420H RTX 3050</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -1506,12 +1515,15 @@
         </is>
       </c>
       <c r="C45" s="6" t="n"/>
+      <c r="D45" t="n">
+        <v>15.4</v>
+      </c>
       <c r="E45" s="9" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15AHP11 R7 250 RTX 5050</t>
+          <t>Lenovo LOQ 15AHP10 RTX 5050</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -1525,7 +1537,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15ARP10E Ryzen 7 170 RTX 3050</t>
+          <t>Lenovo LOQ 15AHP11 R7 250 RTX 5050</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -1533,17 +1545,13 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>https://tk.tokopedia.com/ZS4vF7kpy/</t>
-        </is>
-      </c>
+      <c r="C47" s="6" t="n"/>
       <c r="E47" s="9" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15IRX10 i5-13450HX</t>
+          <t>Lenovo LOQ 15ARP10E Ryzen 7 170 RTX 3050</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -1551,17 +1559,17 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C48" s="6" t="n"/>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>Hot Deals</t>
-        </is>
-      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZS4vF7kpy/</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15IRX10 i7-13700HX</t>
+          <t>Lenovo LOQ 15IRX10 i5-13450HX</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -1570,12 +1578,16 @@
         </is>
       </c>
       <c r="C49" s="6" t="n"/>
-      <c r="E49" s="9" t="n"/>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>Hot Deals</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15IRX9 i5-13450HX</t>
+          <t>Lenovo LOQ 15IRX10 i7-13700HX</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -1589,53 +1601,53 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
+          <t>Lenovo LOQ 15IRX9 i5-13450HX</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n"/>
+      <c r="E51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
           <t>Lenovo LOQ Essential 15ARP10E R7 7735HS</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>https://tk.tokopedia.com/ZS4tEVArt/</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>Hot Deals</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>High Gaming  (24 laptop)</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="17" t="n"/>
-      <c r="D52" s="11" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>Acer Predator Helios Neo 16S Ultra 7 255HX RTX 5060</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>High Gaming</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="n"/>
-      <c r="E53" s="9" t="n"/>
+      <c r="B53" s="14" t="n"/>
+      <c r="C53" s="15" t="n"/>
+      <c r="D53" s="11" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>Acer Predator Helios Neo 16S Ultra 7 356H RTX 5060</t>
+          <t>Acer Predator Helios Neo 16S Ultra 7 255HX RTX 5060</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -1649,7 +1661,7 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>Acer Predator Helios Neo 16S Ultra 9 386H RTX 5070</t>
+          <t>Acer Predator Helios Neo 16S Ultra 7 356H RTX 5060</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -1663,7 +1675,7 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>ASUS ROG Strix G16 2025 G614PR RTX 5070 Ti</t>
+          <t>Acer Predator Helios Neo 16S Ultra 9 386H RTX 5070</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -1677,7 +1689,7 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>ASUS ROG Strix G16 G614PH Ryzen 9 8940HX RTX 5050</t>
+          <t>ASUS ROG Strix G16 2025 G614PR RTX 5070 Ti</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -1691,7 +1703,7 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>ASUS TUF A14 FA401UH Ryzen AI 7 260 RTX 5050</t>
+          <t>ASUS ROG Strix G16 G614PH Ryzen 9 8940HX RTX 5050</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -1705,7 +1717,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>ASUS TUF A16 FA608UM Ryzen AI 7 260 RTX 5060</t>
+          <t>ASUS TUF A14 FA401UH Ryzen AI 7 260 RTX 5050</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -1719,7 +1731,7 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>ASUS TUF A16 FA608UP Ryzen AI 7 260 RTX 5070</t>
+          <t>ASUS TUF A16 FA608UM Ryzen AI 7 260 RTX 5060</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -1733,7 +1745,7 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>Axioo Pongo 765 i7-13620H RTX 5060</t>
+          <t>ASUS TUF A16 FA608UP Ryzen AI 7 260 RTX 5070</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -1747,7 +1759,7 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>Axioo Pongo 765 V2 i7-13700H RTX 5060</t>
+          <t>Axioo Pongo 765 i7-13620H RTX 5060</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -1761,7 +1773,7 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>Axioo Pongo 775 i7-13620H RTX 5070</t>
+          <t>Axioo Pongo 765 V2 i7-13700H RTX 5060</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -1775,7 +1787,7 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>HP Omen i7-14650HX RTX 5060</t>
+          <t>Axioo Pongo 775 i7-13620H RTX 5070</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -1789,7 +1801,7 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>HP Omen Max 16 Ryzen AI 7 350 RTX 5070 Ti</t>
+          <t>HP Omen i7-14650HX RTX 5060</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -1803,7 +1815,7 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>HP Omen Ryzen 9 8940HX RTX 5060</t>
+          <t>HP Omen Max 16 Ryzen AI 7 350 RTX 5070 Ti</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -1814,10 +1826,10 @@
       <c r="C66" s="6" t="n"/>
       <c r="E66" s="9" t="n"/>
     </row>
-    <row r="67" ht="20" customHeight="1" s="19">
+    <row r="67" ht="20" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>Lenovo Legion 5i 15IAX10 Ultra 7 255HX RTX 5060</t>
+          <t>HP Omen Ryzen 9 8940HX RTX 5060</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -1831,7 +1843,7 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>Lenovo Legion 5i 15IRX10 i7-13650HX RTX 5050</t>
+          <t>Lenovo Legion 5i 15IAX10 Ultra 7 255HX RTX 5060</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -1845,7 +1857,7 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>Lenovo Legion 5i 15IRX10 i7-14700HX RTX 5060</t>
+          <t>Lenovo Legion 5i 15IRX10 i7-13650HX RTX 5050</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -1859,7 +1871,7 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>Lenovo Legion 5i 15IRX10 OLED RTX 5050</t>
+          <t>Lenovo Legion 5i 15IRX10 i7-14700HX RTX 5060</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -1873,7 +1885,7 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5i 16 OLED Ultra 9 275HX RTX 5070 Ti</t>
+          <t>Lenovo Legion 5i 15IRX10 OLED RTX 5050</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -1887,7 +1899,7 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15AHP11 Ryzen AI 7 250 RTX 5060</t>
+          <t>Lenovo Legion Pro 5i 16 OLED Ultra 9 275HX RTX 5070 Ti</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -1901,7 +1913,7 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>MSI Crosshair A16 HX Ryzen 9 7945HX RTX 5060</t>
+          <t>Lenovo LOQ 15AHP11 Ryzen AI 7 250 RTX 5060</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -1915,7 +1927,7 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>MSI Crosshair A16 HX Ryzen 9 7945HX RTX 5070</t>
+          <t>MSI Crosshair A16 HX Ryzen 9 7945HX RTX 5060</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -1929,7 +1941,7 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>MSI Vector 16HX Ultra 7 255HX RTX 5070 Ti</t>
+          <t>MSI Crosshair A16 HX Ryzen 9 7945HX RTX 5070</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -1943,7 +1955,7 @@
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>MSI Vector 16HX Ultra 9 275HX RTX 5080</t>
+          <t>MSI Vector 16HX Ultra 7 255HX RTX 5070 Ti</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -1955,33 +1967,33 @@
       <c r="E76" s="9" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="15" t="inlineStr">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>MSI Vector 16HX Ultra 9 275HX RTX 5080</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>High Gaming</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="n"/>
+      <c r="E77" s="9" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
         <is>
           <t>Ultrabook  (20 laptop)</t>
         </is>
       </c>
-      <c r="B77" s="16" t="n"/>
-      <c r="C77" s="17" t="n"/>
-      <c r="D77" s="11" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t>Acer Swift 14 OLED Core Ultra 5 226V</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>Ultrabook</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="n"/>
-      <c r="E78" s="9" t="n"/>
+      <c r="B78" s="14" t="n"/>
+      <c r="C78" s="15" t="n"/>
+      <c r="D78" s="11" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>Acer Swift Air 14 Core Ultra 5 125H</t>
+          <t>Acer Swift 14 OLED Core Ultra 5 226V</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -1995,7 +2007,7 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>Acer Swift Air 14 Core Ultra 7 155H</t>
+          <t>Acer Swift Air 14 Core Ultra 5 125H</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -2009,7 +2021,7 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>Acer Swift Go 14 AI SFG14-171 Ultra 7 358H</t>
+          <t>Acer Swift Air 14 Core Ultra 7 155H</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -2023,7 +2035,7 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>Acer Swift Go 14 AI SFG14-73-73P9</t>
+          <t>Acer Swift Go 14 AI SFG14-171 Ultra 7 358H</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -2031,21 +2043,13 @@
           <t>Ultrabook</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>https://tk.tokopedia.com/ZS4tos6XL/</t>
-        </is>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>Hot Deals</t>
-        </is>
-      </c>
+      <c r="C82" s="6" t="n"/>
+      <c r="E82" s="9" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>Acer Swift Go 14 SFG14 Ultra 5 125H</t>
+          <t>Acer Swift Go 14 AI SFG14-73-73P9</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -2053,13 +2057,21 @@
           <t>Ultrabook</t>
         </is>
       </c>
-      <c r="C83" s="6" t="n"/>
-      <c r="E83" s="9" t="n"/>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZS4tos6XL/</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>Hot Deals</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>Advan Workplus AI Ryzen 7 255</t>
+          <t>Acer Swift Go 14 SFG14 Ultra 5 125H</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -2073,7 +2085,7 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>Apple MacBook Air M2 13&amp;quot;</t>
+          <t>Advan Workplus AI Ryzen 7 255</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -2087,7 +2099,7 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>Apple MacBook Air M4</t>
+          <t>Apple MacBook Air M2 13&amp;quot;</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -2101,7 +2113,7 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>Apple MacBook Pro 14 M5</t>
+          <t>Apple MacBook Air M4</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
@@ -2115,7 +2127,7 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>ASUS ExpertBook B9400CBA Ultra 7 358H</t>
+          <t>Apple MacBook Pro 14 M5</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -2129,7 +2141,7 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>ASUS ExpertBook Ultra P5405CSA Ultra 7 258V</t>
+          <t>ASUS ExpertBook B9400CBA Ultra 7 358H</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -2143,7 +2155,7 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14 Ryzen 7 260</t>
+          <t>ASUS ExpertBook Ultra P5405CSA Ultra 7 258V</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -2157,7 +2169,7 @@
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>HP OmniBook 3 14 Core 3 100U</t>
+          <t>ASUS Vivobook S14 Ryzen 7 260</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -2166,15 +2178,12 @@
         </is>
       </c>
       <c r="C91" s="6" t="n"/>
-      <c r="D91" t="n">
-        <v>12.5</v>
-      </c>
       <c r="E91" s="9" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5 14 OLED Ryzen 7 8845HS</t>
+          <t>HP OmniBook 3 14 Core 3 100U</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -2183,12 +2192,15 @@
         </is>
       </c>
       <c r="C92" s="6" t="n"/>
+      <c r="D92" t="n">
+        <v>12.5</v>
+      </c>
       <c r="E92" s="9" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5 14IAH10 Ultra 5 225H</t>
+          <t>Lenovo IdeaPad Slim 5 14 OLED Ryzen 7 8845HS</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -2202,7 +2214,7 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5i Ultra 7 255H</t>
+          <t>Lenovo IdeaPad Slim 5 14IAH10 Ultra 5 225H</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -2216,7 +2228,7 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7i Aura Edition Ultra 5 226V</t>
+          <t>Lenovo IdeaPad Slim 5i Ultra 7 255H</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -2230,7 +2242,7 @@
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>MSI Prestige 14 AI+ Ultra 7 355</t>
+          <t>Lenovo Yoga Slim 7i Aura Edition Ultra 5 226V</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -2244,7 +2256,7 @@
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>MSI Prestige 14 Flip AI+ Ultra 9 386H</t>
+          <t>MSI Prestige 14 AI+ Ultra 7 355</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -2255,13 +2267,27 @@
       <c r="C97" s="6" t="n"/>
       <c r="E97" s="9" t="n"/>
     </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>MSI Prestige 14 Flip AI+ Ultra 9 386H</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Ultrabook</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="n"/>
+      <c r="E98" s="9" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="A53:C53"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A52:C52"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
@@ -2289,15 +2315,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2312,13 +2341,13 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="54" customWidth="1" style="19" min="1" max="1"/>
-    <col width="18" customWidth="1" style="19" min="2" max="2"/>
-    <col width="46" customWidth="1" style="19" min="3" max="3"/>
-    <col width="26" customWidth="1" style="19" min="4" max="4"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" s="19">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Laptop</t>
@@ -2534,13 +2563,13 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="54" customWidth="1" style="19" min="1" max="1"/>
-    <col width="18" customWidth="1" style="19" min="2" max="2"/>
-    <col width="46" customWidth="1" style="19" min="3" max="3"/>
-    <col width="26" customWidth="1" style="19" min="4" max="4"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" s="19">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Laptop</t>
@@ -2825,16 +2854,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="54" customWidth="1" style="19" min="1" max="1"/>
-    <col width="18" customWidth="1" style="19" min="2" max="2"/>
-    <col width="46" customWidth="1" style="19" min="3" max="3"/>
-    <col width="26" customWidth="1" style="19" min="4" max="4"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" s="19">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Laptop</t>
@@ -2961,7 +2990,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Acer Nitro V15 RTX 5050 i5-13420H</t>
+          <t>Acer Nitro V15 Core 5 210H RTX 3050</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -2969,21 +2998,13 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>https://tk.tokopedia.com/ZS4too9ra/</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Hot Deals</t>
-        </is>
-      </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>ASUS Gaming V16 V3607VH Core 5 210H</t>
+          <t>Acer Nitro V15 RTX 5050 i5-13420H</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -2991,13 +3012,21 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="9" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZS4too9ra/</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Hot Deals</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>ASUS TUF A15 FA506NCG</t>
+          <t>ASUS Gaming V16 V3607VH Core 5 210H</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -3005,17 +3034,13 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>https://tk.tokopedia.com/ZSVrEvhme/</t>
-        </is>
-      </c>
+      <c r="C9" s="6" t="n"/>
       <c r="D9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>ASUS TUF A16 FA608UH RTX 5050</t>
+          <t>ASUS TUF A15 FA506NCG</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -3025,7 +3050,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>https://tk.tokopedia.com/ZSVrEtTrs/</t>
+          <t>https://tk.tokopedia.com/ZSVrEvhme/</t>
         </is>
       </c>
       <c r="D10" s="9" t="n"/>
@@ -3033,7 +3058,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>ASUS TUF Gaming A16 FA607NUG</t>
+          <t>ASUS TUF A16 FA608UH RTX 5050</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -3043,7 +3068,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>https://tk.tokopedia.com/ZSVroFR3P/</t>
+          <t>https://tk.tokopedia.com/ZSVrEtTrs/</t>
         </is>
       </c>
       <c r="D11" s="9" t="n"/>
@@ -3051,7 +3076,7 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Axioo Pongo 535 i5-13420H RTX 3050</t>
+          <t>ASUS TUF Gaming A16 FA607NUG</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -3059,13 +3084,17 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVroFR3P/</t>
+        </is>
+      </c>
       <c r="D12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Axioo Pongo 735 i7-13620H RTX 3050</t>
+          <t>Axioo Pongo 535 i5-13420H RTX 3050</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -3079,7 +3108,7 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Axioo Pongo 750 i7-13620H RTX 4050</t>
+          <t>Axioo Pongo 735 i7-13620H RTX 3050</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -3089,7 +3118,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>https://tk.tokopedia.com/ZS4vFaySC/</t>
+          <t>https://tk.tokopedia.com/ZSVUSQLfk/</t>
         </is>
       </c>
       <c r="D14" s="9" t="n"/>
@@ -3097,7 +3126,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Axioo Pongo 755-X72 R7 255 RTX 5050</t>
+          <t>Axioo Pongo 750 i7-13620H RTX 4050</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -3105,17 +3134,17 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Hot Deals</t>
-        </is>
-      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVUSqCs3/</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Colorful Evol P15 HE55D i5-12450H</t>
+          <t>Axioo Pongo 755-X72 R7 255 RTX 5050</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -3125,7 +3154,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>https://tk.tokopedia.com/ZS4tEaS7p/</t>
+          <t>https://tk.tokopedia.com/ZSVUSnmBv/</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -3137,7 +3166,7 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Colorful Evol P15 RTX 5050</t>
+          <t>Colorful Evol P15 HE55D i5-12450H</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -3145,7 +3174,11 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZS4tEaS7p/</t>
+        </is>
+      </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Hot Deals</t>
@@ -3155,7 +3188,7 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>HP Victus 15 FA2717TX i5-13420H</t>
+          <t>Colorful Evol P15 RTX 5050</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -3163,13 +3196,21 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="9" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZSVUADx7M/</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Hot Deals</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>HP Victus 15 i5-13420H RTX 3050</t>
+          <t>HP Victus 15 FA2717TX i5-13420H</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -3183,7 +3224,7 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15AHP10 RTX 5050</t>
+          <t>HP Victus 15 i5-13420H RTX 3050</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -3197,7 +3238,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15AHP11 R7 250 RTX 5050</t>
+          <t>Lenovo LOQ 15AHP10 RTX 5050</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -3211,7 +3252,7 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15ARP10E Ryzen 7 170 RTX 3050</t>
+          <t>Lenovo LOQ 15AHP11 R7 250 RTX 5050</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -3219,17 +3260,13 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>https://tk.tokopedia.com/ZS4vF7kpy/</t>
-        </is>
-      </c>
+      <c r="C22" s="6" t="n"/>
       <c r="D22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15IRX10 i5-13450HX</t>
+          <t>Lenovo LOQ 15ARP10E Ryzen 7 170 RTX 3050</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -3237,17 +3274,17 @@
           <t>Gaming</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Hot Deals</t>
-        </is>
-      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>https://tk.tokopedia.com/ZS4vF7kpy/</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15IRX10 i7-13700HX</t>
+          <t>Lenovo LOQ 15IRX10 i5-13450HX</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -3256,12 +3293,16 @@
         </is>
       </c>
       <c r="C24" s="6" t="n"/>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Hot Deals</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 15IRX9 i5-13450HX</t>
+          <t>Lenovo LOQ 15IRX10 i7-13700HX</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -3275,20 +3316,34 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
+          <t>Lenovo LOQ 15IRX9 i5-13450HX</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
           <t>Lenovo LOQ Essential 15ARP10E R7 7735HS</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Gaming</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>https://tk.tokopedia.com/ZS4tEVArt/</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>Hot Deals</t>
         </is>
@@ -3301,14 +3356,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3323,13 +3381,13 @@
   <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="54" customWidth="1" style="19" min="1" max="1"/>
-    <col width="18" customWidth="1" style="19" min="2" max="2"/>
-    <col width="46" customWidth="1" style="19" min="3" max="3"/>
-    <col width="26" customWidth="1" style="19" min="4" max="4"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" s="19">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Laptop</t>
@@ -3677,13 +3735,13 @@
   <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="54" customWidth="1" style="19" min="1" max="1"/>
-    <col width="18" customWidth="1" style="19" min="2" max="2"/>
-    <col width="46" customWidth="1" style="19" min="3" max="3"/>
-    <col width="26" customWidth="1" style="19" min="4" max="4"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" s="19">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Laptop</t>
@@ -3991,8 +4049,8 @@
   <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="26" customWidth="1" style="19" min="1" max="1"/>
-    <col width="74" customWidth="1" style="19" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="74" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4075,7 +4133,7 @@
       <c r="A8" s="3" t="n"/>
       <c r="B8" s="2" t="n"/>
     </row>
-    <row r="9" ht="28" customHeight="1" s="19">
+    <row r="9" ht="28" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
           <t>Cara mengisi</t>
@@ -4151,7 +4209,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1" s="19">
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="3" t="n"/>
       <c r="B17" s="2" t="inlineStr">
         <is>

--- a/LAPTOP_TANPA_LINK_AFFILIATE.xlsx
+++ b/LAPTOP_TANPA_LINK_AFFILIATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cahya\OneDrive\Documents\Claude\Projects\astro-laptop-latihan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8675719-7450-4E4F-8DE4-0BE603DE7C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61AEDAF-7A4B-4512-899F-5681D4A4EA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -815,7 +815,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -841,20 +841,15 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1186,11 +1181,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="19"/>
       <c r="D2" s="11" t="s">
         <v>6</v>
       </c>
@@ -1333,11 +1328,11 @@
       <c r="E11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -1533,11 +1528,11 @@
       <c r="E25" s="9"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="19"/>
       <c r="D26" s="11"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -1812,10 +1807,10 @@
       <c r="B45" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C45" s="20" t="s">
+      <c r="C45" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="D45" s="21">
+      <c r="D45">
         <v>15.4</v>
       </c>
       <c r="E45" s="9"/>
@@ -1827,10 +1822,9 @@
       <c r="B46" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C46" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D46" s="21"/>
       <c r="E46" s="9"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -1840,10 +1834,10 @@
       <c r="B47" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C47" s="20" t="s">
+      <c r="C47" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="D47" s="21">
+      <c r="D47">
         <v>23.6</v>
       </c>
       <c r="E47" s="9"/>
@@ -1855,10 +1849,9 @@
       <c r="B48" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C48" s="20" t="s">
+      <c r="C48" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="D48" s="21"/>
       <c r="E48" s="9"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
@@ -1868,10 +1861,9 @@
       <c r="B49" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C49" s="20" t="s">
+      <c r="C49" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D49" s="21"/>
       <c r="E49" s="9" t="s">
         <v>11</v>
       </c>
@@ -1883,10 +1875,10 @@
       <c r="B50" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C50" s="20" t="s">
+      <c r="C50" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D50" s="21">
+      <c r="D50">
         <v>24.5</v>
       </c>
       <c r="E50" s="9"/>
@@ -1898,10 +1890,10 @@
       <c r="B51" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C51" s="20" t="s">
+      <c r="C51" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="D51" s="21">
+      <c r="D51">
         <v>17.899999999999999</v>
       </c>
       <c r="E51" s="9"/>
@@ -1916,18 +1908,17 @@
       <c r="C52" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D52" s="21"/>
       <c r="E52" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="B53" s="17"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="22"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="11"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
@@ -1936,10 +1927,10 @@
       <c r="B54" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="D54" s="21">
+      <c r="D54">
         <v>26.5</v>
       </c>
       <c r="E54" s="9"/>
@@ -1951,10 +1942,10 @@
       <c r="B55" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="D55" s="21">
+      <c r="D55">
         <v>35.5</v>
       </c>
       <c r="E55" s="9"/>
@@ -1969,7 +1960,7 @@
       <c r="C56" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="D56" s="10">
+      <c r="D56" s="21">
         <v>35</v>
       </c>
       <c r="E56" s="9"/>
@@ -1981,7 +1972,8 @@
       <c r="B57" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C57" s="6"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="21"/>
       <c r="E57" s="9"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
@@ -1991,10 +1983,10 @@
       <c r="B58" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D58" s="10">
+      <c r="D58" s="21">
         <v>43</v>
       </c>
       <c r="E58" s="9"/>
@@ -2006,10 +1998,10 @@
       <c r="B59" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="C59" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="D59" s="10">
+      <c r="D59" s="21">
         <v>30.8</v>
       </c>
       <c r="E59" s="9"/>
@@ -2021,10 +2013,10 @@
       <c r="B60" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="D60" s="10">
+      <c r="D60" s="21">
         <v>26.8</v>
       </c>
       <c r="E60" s="9"/>
@@ -2036,10 +2028,10 @@
       <c r="B61" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C61" s="23" t="s">
+      <c r="C61" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="D61" s="10">
+      <c r="D61" s="21">
         <v>28</v>
       </c>
       <c r="E61" s="9"/>
@@ -2051,10 +2043,10 @@
       <c r="B62" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="D62" s="24">
+      <c r="D62" s="21">
         <v>29.5</v>
       </c>
       <c r="E62" s="9"/>
@@ -2066,10 +2058,10 @@
       <c r="B63" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="C63" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="D63" s="24">
+      <c r="D63" s="21">
         <v>21.3</v>
       </c>
       <c r="E63" s="9"/>
@@ -2081,10 +2073,10 @@
       <c r="B64" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="D64" s="24">
+      <c r="D64" s="21">
         <v>22.6</v>
       </c>
       <c r="E64" s="9"/>
@@ -2096,10 +2088,10 @@
       <c r="B65" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="D65" s="24">
+      <c r="D65" s="21">
         <v>24.8</v>
       </c>
       <c r="E65" s="9"/>
@@ -2111,7 +2103,8 @@
       <c r="B66" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="21"/>
       <c r="E66" s="9"/>
     </row>
     <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -2121,10 +2114,10 @@
       <c r="B67" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D67" s="24">
+      <c r="D67" s="21">
         <v>38</v>
       </c>
       <c r="E67" s="9"/>
@@ -2136,10 +2129,10 @@
       <c r="B68" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="D68" s="24">
+      <c r="D68" s="21">
         <v>25.2</v>
       </c>
       <c r="E68" s="9"/>
@@ -2151,10 +2144,10 @@
       <c r="B69" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C69" s="13" t="s">
+      <c r="C69" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="D69" s="24">
+      <c r="D69" s="21">
         <v>35.299999999999997</v>
       </c>
       <c r="E69" s="9" t="s">
@@ -2168,10 +2161,10 @@
       <c r="B70" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="D70" s="24">
+      <c r="D70" s="21">
         <v>25.8</v>
       </c>
       <c r="E70" s="9"/>
@@ -2183,10 +2176,10 @@
       <c r="B71" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="D71" s="10">
+      <c r="D71" s="21">
         <v>28.3</v>
       </c>
       <c r="E71" s="9" t="s">
@@ -2200,9 +2193,10 @@
       <c r="B72" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C72" s="13" t="s">
+      <c r="C72" s="16" t="s">
         <v>199</v>
       </c>
+      <c r="D72" s="21"/>
       <c r="E72" s="9"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
@@ -2212,10 +2206,10 @@
       <c r="B73" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="C73" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="D73" s="10">
+      <c r="D73" s="21">
         <v>44</v>
       </c>
       <c r="E73" s="9"/>
@@ -2227,10 +2221,10 @@
       <c r="B74" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C74" s="13" t="s">
+      <c r="C74" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="D74" s="10">
+      <c r="D74" s="21">
         <v>26.8</v>
       </c>
       <c r="E74" s="9"/>
@@ -2242,10 +2236,10 @@
       <c r="B75" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C75" s="23" t="s">
+      <c r="C75" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="D75" s="10">
+      <c r="D75" s="21">
         <v>24</v>
       </c>
       <c r="E75" s="9"/>
@@ -2257,9 +2251,10 @@
       <c r="B76" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C76" s="13" t="s">
+      <c r="C76" s="16" t="s">
         <v>203</v>
       </c>
+      <c r="D76" s="21"/>
       <c r="E76" s="9"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
@@ -2269,10 +2264,10 @@
       <c r="B77" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C77" s="13" t="s">
+      <c r="C77" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="D77" s="24">
+      <c r="D77" s="21">
         <v>35</v>
       </c>
       <c r="E77" s="9"/>
@@ -2284,20 +2279,20 @@
       <c r="B78" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C78" s="13" t="s">
+      <c r="C78" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="D78" s="24">
+      <c r="D78" s="21">
         <v>44.2</v>
       </c>
       <c r="E78" s="9"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="B79" s="17"/>
-      <c r="C79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="19"/>
       <c r="D79" s="11"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">

--- a/LAPTOP_TANPA_LINK_AFFILIATE.xlsx
+++ b/LAPTOP_TANPA_LINK_AFFILIATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cahya\OneDrive\Documents\Claude\Projects\astro-laptop-latihan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61AEDAF-7A4B-4512-899F-5681D4A4EA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167B3B95-E71E-4B2E-8212-B288429064AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="224">
   <si>
     <t>Laptop</t>
   </si>
@@ -644,6 +644,60 @@
   </si>
   <si>
     <t>https://tk.tokopedia.com/ZSVfjfjAj/</t>
+  </si>
+  <si>
+    <t>https://tk.tokopedia.com/ZSVfMpVce/</t>
+  </si>
+  <si>
+    <t>https://tk.tokopedia.com/ZSVfrYpff/</t>
+  </si>
+  <si>
+    <t>https://tk.tokopedia.com/ZSVfMoy9f/</t>
+  </si>
+  <si>
+    <t>Varian WUXGA</t>
+  </si>
+  <si>
+    <t>https://tk.tokopedia.com/ZSVfrUnSC/</t>
+  </si>
+  <si>
+    <t>https://tk.tokopedia.com/ZSVfrDmoA/</t>
+  </si>
+  <si>
+    <t>https://tk.tokopedia.com/ZSVfr7c2H/</t>
+  </si>
+  <si>
+    <t>https://tk.tokopedia.com/ZSVfhMMVs/</t>
+  </si>
+  <si>
+    <t>Varian yang ada ASUS EXPERTBOOK B9406CAA</t>
+  </si>
+  <si>
+    <t>https://tk.tokopedia.com/ZSVfrKbYg/</t>
+  </si>
+  <si>
+    <t>https://tk.tokopedia.com/ZSVfhVrwB/</t>
+  </si>
+  <si>
+    <t>https://tk.tokopedia.com/ZSVfhxyWp/</t>
+  </si>
+  <si>
+    <t>https://tk.tokopedia.com/ZSVfhD7eE/</t>
+  </si>
+  <si>
+    <t>https://tk.tokopedia.com/ZSVfhPDhQ/</t>
+  </si>
+  <si>
+    <t>https://tk.tokopedia.com/ZSVfhH3fL/</t>
+  </si>
+  <si>
+    <t>https://tk.tokopedia.com/ZSVfhswsx/</t>
+  </si>
+  <si>
+    <t>https://tk.tokopedia.com/ZSVfhWmAX/</t>
+  </si>
+  <si>
+    <t>https://tk.tokopedia.com/ZSVfke8g2/</t>
   </si>
 </sst>
 </file>
@@ -815,7 +869,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -850,6 +904,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2302,7 +2358,12 @@
       <c r="B80" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="D80" s="23">
+        <v>15.7</v>
+      </c>
       <c r="E80" s="9"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
@@ -2312,8 +2373,15 @@
       <c r="B81" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C81" s="6"/>
-      <c r="E81" s="9"/>
+      <c r="C81" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="D81" s="23">
+        <v>16.7</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="8" t="s">
@@ -2322,7 +2390,12 @@
       <c r="B82" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C82" s="6"/>
+      <c r="C82" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="D82" s="10">
+        <v>15.4</v>
+      </c>
       <c r="E82" s="9"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
@@ -2332,7 +2405,12 @@
       <c r="B83" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C83" s="6"/>
+      <c r="C83" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="D83" s="10">
+        <v>25</v>
+      </c>
       <c r="E83" s="9"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
@@ -2342,7 +2420,7 @@
       <c r="B84" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C84" s="6" t="s">
+      <c r="C84" s="22" t="s">
         <v>144</v>
       </c>
       <c r="E84" s="9" t="s">
@@ -2356,7 +2434,12 @@
       <c r="B85" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C85" s="6"/>
+      <c r="C85" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="D85" s="10">
+        <v>12.5</v>
+      </c>
       <c r="E85" s="9"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
@@ -2366,7 +2449,12 @@
       <c r="B86" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="D86" s="23">
+        <v>10.199999999999999</v>
+      </c>
       <c r="E86" s="9"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
@@ -2406,8 +2494,15 @@
       <c r="B90" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C90" s="6"/>
-      <c r="E90" s="9"/>
+      <c r="C90" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="D90" s="10">
+        <v>48</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="8" t="s">
@@ -2416,7 +2511,12 @@
       <c r="B91" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C91" s="6"/>
+      <c r="C91" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="D91" s="10">
+        <v>21</v>
+      </c>
       <c r="E91" s="9"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
@@ -2426,7 +2526,12 @@
       <c r="B92" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C92" s="6"/>
+      <c r="C92" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="D92" s="10">
+        <v>17.3</v>
+      </c>
       <c r="E92" s="9"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
@@ -2436,8 +2541,10 @@
       <c r="B93" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C93" s="6"/>
-      <c r="D93">
+      <c r="C93" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D93" s="10">
         <v>12.5</v>
       </c>
       <c r="E93" s="9"/>
@@ -2449,7 +2556,12 @@
       <c r="B94" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C94" s="6"/>
+      <c r="C94" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="D94" s="10">
+        <v>17.7</v>
+      </c>
       <c r="E94" s="9"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
@@ -2459,7 +2571,12 @@
       <c r="B95" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C95" s="6"/>
+      <c r="C95" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="D95" s="10">
+        <v>18.2</v>
+      </c>
       <c r="E95" s="9"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
@@ -2469,7 +2586,12 @@
       <c r="B96" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C96" s="6"/>
+      <c r="C96" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="D96" s="10">
+        <v>20</v>
+      </c>
       <c r="E96" s="9"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
@@ -2479,7 +2601,12 @@
       <c r="B97" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C97" s="6"/>
+      <c r="C97" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="D97" s="10">
+        <v>19</v>
+      </c>
       <c r="E97" s="9"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
@@ -2489,7 +2616,12 @@
       <c r="B98" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C98" s="6"/>
+      <c r="C98" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="D98" s="10">
+        <v>34</v>
+      </c>
       <c r="E98" s="9"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
@@ -2499,7 +2631,12 @@
       <c r="B99" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C99" s="6"/>
+      <c r="C99" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="D99" s="10">
+        <v>31.2</v>
+      </c>
       <c r="E99" s="9"/>
     </row>
   </sheetData>
